--- a/esyluban/examples/dev/DataTables/__enums__.xlsx
+++ b/esyluban/examples/dev/DataTables/__enums__.xlsx
@@ -1351,7 +1351,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="H1:L1"/>
+    <mergeCell ref="H2:L2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
